--- a/output/pdf_financials_xlsx/QREE.xlsx
+++ b/output/pdf_financials_xlsx/QREE.xlsx
@@ -726,13 +726,13 @@
         </is>
       </c>
       <c r="C16" s="3" t="n">
-        <v>8.7486</v>
+        <v>-8.7486</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>0.2084</v>
+        <v>-0.2084</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>0.6735</v>
+        <v>-0.6735</v>
       </c>
     </row>
     <row r="17">
@@ -820,13 +820,13 @@
         </is>
       </c>
       <c r="C20" s="3" t="n">
-        <v>8.7486</v>
+        <v>-8.7486</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>0.2084</v>
+        <v>-0.2084</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>0.6735</v>
+        <v>-0.6735</v>
       </c>
     </row>
     <row r="21">
@@ -879,13 +879,13 @@
         </is>
       </c>
       <c r="C23" s="3" t="n">
-        <v>8.7486</v>
+        <v>-8.7486</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>0.2084</v>
+        <v>-0.2084</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>0.6735</v>
+        <v>-0.6735</v>
       </c>
     </row>
     <row r="24">
@@ -938,7 +938,7 @@
         </is>
       </c>
       <c r="C26" s="3" t="n">
-        <v>-16.506792</v>
+        <v>16.506792</v>
       </c>
       <c r="D26" s="1" t="inlineStr">
         <is>
@@ -963,13 +963,13 @@
         </is>
       </c>
       <c r="C27" s="3" t="n">
-        <v>8.7486</v>
+        <v>-8.7486</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>0.2084</v>
+        <v>-0.2084</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>0.6735</v>
+        <v>-0.6735</v>
       </c>
     </row>
     <row r="28">
@@ -1003,13 +1003,13 @@
         </is>
       </c>
       <c r="C29" s="3" t="n">
-        <v>8.7486</v>
+        <v>-8.7486</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>0.2084</v>
+        <v>-0.2084</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>0.6735</v>
+        <v>-0.6735</v>
       </c>
     </row>
     <row r="30">
@@ -1051,13 +1051,13 @@
         </is>
       </c>
       <c r="C31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="32">
@@ -2219,16 +2219,16 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>3.023111</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>3.0231</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>3.0231</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>3.6224</v>
       </c>
     </row>
     <row r="93">
@@ -2709,10 +2709,10 @@
         <v>7.9005</v>
       </c>
       <c r="D118" s="3" t="n">
-        <v>0.015</v>
+        <v>0.0086</v>
       </c>
       <c r="E118" s="3" t="n">
-        <v>-0.02</v>
+        <v>-0.2594</v>
       </c>
     </row>
     <row r="119">
@@ -3514,7 +3514,11 @@
           <t>Reserves 10</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr"/>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E13" t="inlineStr">
         <is>
           <t>-</t>
@@ -4308,7 +4312,11 @@
           <t>Reserves 14</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr"/>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E35" s="5" t="n">
         <v>3.023111</v>
       </c>
@@ -4800,7 +4808,11 @@
           <t>Exploration and evaluation asset expenditures</t>
         </is>
       </c>
-      <c r="D49" t="inlineStr"/>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E49" t="inlineStr">
         <is>
           <t>-</t>
@@ -6653,13 +6665,13 @@
         </is>
       </c>
       <c r="F100" s="5" t="n">
-        <v>8.7486</v>
+        <v>-8.7486</v>
       </c>
       <c r="G100" s="5" t="n">
-        <v>0.2084</v>
+        <v>-0.2084</v>
       </c>
       <c r="H100" s="5" t="n">
-        <v>0.6735</v>
+        <v>-0.6735</v>
       </c>
     </row>
     <row r="101">

--- a/output/pdf_financials_xlsx/QREE.xlsx
+++ b/output/pdf_financials_xlsx/QREE.xlsx
@@ -605,10 +605,10 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>1.043289</v>
+        <v>2.025607</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>0.2604</v>
+        <v>0.399062</v>
       </c>
       <c r="D10" s="3" t="n">
         <v>0.1287</v>
@@ -645,13 +645,13 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.005176</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>-0.0046</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>-0.0022</v>
       </c>
       <c r="E12" s="3" t="n">
         <v>0</v>
@@ -963,10 +963,10 @@
         </is>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-8.7486</v>
+        <v>-8.744</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-0.2084</v>
+        <v>-0.2062</v>
       </c>
       <c r="E27" s="3" t="n">
         <v>-0.6735</v>
@@ -1003,10 +1003,10 @@
         </is>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-8.7486</v>
+        <v>-8.744</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-0.2084</v>
+        <v>-0.2062</v>
       </c>
       <c r="E29" s="3" t="n">
         <v>-0.6735</v>
@@ -1101,16 +1101,16 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.867073</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.2115</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.07149999999999999</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.6239</v>
       </c>
     </row>
     <row r="35">
@@ -1139,16 +1139,16 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.867073</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.2115</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.07149999999999999</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.6239</v>
       </c>
     </row>
     <row r="37">
@@ -1367,16 +1367,16 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.9735239999999999</v>
+        <v>0.106451</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.2308</v>
+        <v>0.0193</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.0759</v>
+        <v>0.0044</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.6277</v>
+        <v>0.0038</v>
       </c>
     </row>
     <row r="49">
@@ -3126,7 +3126,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -3790,7 +3790,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E21" s="5" t="n">
@@ -6910,7 +6910,7 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -7170,14 +7170,14 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E114" s="5" t="n">
-        <v>-2.025607</v>
+        <v>2.025607</v>
       </c>
       <c r="F114" s="5" t="n">
-        <v>-0.399062</v>
+        <v>0.399062</v>
       </c>
       <c r="G114" t="inlineStr">
         <is>
@@ -7242,7 +7242,7 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E116" s="5" t="n">

--- a/output/pdf_financials_xlsx/QREE.xlsx
+++ b/output/pdf_financials_xlsx/QREE.xlsx
@@ -1218,7 +1218,7 @@
         <v>0</v>
       </c>
       <c r="C40" s="3" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="D40" s="3" t="n">
         <v>0</v>
